--- a/4. Screener/ControlFile_Screener.xlsx
+++ b/4. Screener/ControlFile_Screener.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHussain\Dropbox (IRENA)\01 My work folder\2. MSR\20210105 zoning codes\2. MSR_OpenRepo\4. Screener\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\4. Screener\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E0C431-DAB1-4EC8-AFA2-5F49F6C905F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19310" windowHeight="6290"/>
+    <workbookView xWindow="23880" yWindow="-6870" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PathsAndConfig" sheetId="8" r:id="rId1"/>
@@ -25,26 +26,20 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={53B51DBE-FF07-406B-823A-4F8310867827}</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -68,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="112">
   <si>
     <t>Index</t>
   </si>
@@ -277,21 +272,9 @@
     <t>Address to region boundaries shapefile</t>
   </si>
   <si>
-    <t>C:\Users\BHussain\Documents\Bilal\Results-Prescreen\SolarPV_prescreen.shp</t>
-  </si>
-  <si>
-    <t>C:\Users\BHussain\Documents\Bilal\MSRHomeDirectory\InputDataSets\AfricaUNCompliantGAUL52CountryBoundaries.shp</t>
-  </si>
-  <si>
     <t>MSR covered area cutoff (%)</t>
   </si>
   <si>
-    <t>C:\Users\BHussain\Documents\Bilal\Results-Screened</t>
-  </si>
-  <si>
-    <t>C:\Users\BHussain\Documents\Bilal\Results-Prescreen\Wind_prescreen.shp</t>
-  </si>
-  <si>
     <t>Comments</t>
   </si>
   <si>
@@ -328,17 +311,305 @@
     <t>Options=[0-No, 1-Yes]</t>
   </si>
   <si>
-    <t>C:\Users\BHussain\Dropbox (IRENA)\01 My work folder\2. MSR\20210105 zoning codes\2. MSR_OpenRepo\countrynames.csv</t>
-  </si>
-  <si>
-    <t>C:\Users\BHussain\Documents\Bilal\ProfileGeneratorOutputs\Results_LocalTimeProfiles</t>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>Honduras</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
+    <t>Belize</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Guyana</t>
+  </si>
+  <si>
+    <t>Suriname</t>
+  </si>
+  <si>
+    <t>French Guiana</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Peru</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
+    <t>Cuba</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>Dominican Republic</t>
+  </si>
+  <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>countrynames</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.csv</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\3. Attributor and ShapeFileCombiner\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Results-Prescreen_Bolivia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\SolarPV_prescreen.shp</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\3. Attributor and ShapeFileCombiner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\Results-Prescreen_Bolivia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\Wind_prescreen.shp</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. MSR Creator\Input\AllCountryBoundaries_GAUL.shp</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\4. Screener\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Results-Screened_Bolivia</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\2. Profile Generator\</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Output_Bolivia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\Results_LocalTimeProfiles</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,6 +621,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -407,7 +685,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -719,104 +997,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.1796875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="46.453125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="43.7265625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="53.140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="43.7109375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="58" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="B3" s="6" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
@@ -825,7 +1103,7 @@
       </c>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>61</v>
       </c>
@@ -834,7 +1112,7 @@
       </c>
       <c r="C10" s="5"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>58</v>
       </c>
@@ -842,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>59</v>
       </c>
@@ -853,10 +1131,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>62</v>
       </c>
@@ -872,16 +1150,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="66.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -895,7 +1173,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -917,23 +1195,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -941,7 +1219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -949,7 +1227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -957,7 +1235,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -965,7 +1243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -973,7 +1251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -981,7 +1259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -989,7 +1267,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>46</v>
       </c>
@@ -997,7 +1275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -1005,7 +1283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
@@ -1013,7 +1291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
@@ -1021,7 +1299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>47</v>
       </c>
@@ -1029,7 +1307,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1037,7 +1315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -1045,7 +1323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -1053,7 +1331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -1061,7 +1339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -1069,7 +1347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -1077,7 +1355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -1085,7 +1363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
@@ -1093,7 +1371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1101,7 +1379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1109,7 +1387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
@@ -1117,7 +1395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
@@ -1125,7 +1403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
@@ -1133,7 +1411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
@@ -1141,7 +1419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1149,7 +1427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
@@ -1157,7 +1435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
@@ -1165,7 +1443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
@@ -1173,7 +1451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
@@ -1181,7 +1459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
@@ -1189,7 +1467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
@@ -1197,7 +1475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>34</v>
       </c>
@@ -1205,7 +1483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>35</v>
       </c>
@@ -1213,7 +1491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
@@ -1221,7 +1499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -1229,7 +1507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
@@ -1237,7 +1515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>39</v>
       </c>
@@ -1245,7 +1523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
@@ -1253,7 +1531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>52</v>
       </c>
@@ -1261,7 +1539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>49</v>
       </c>
@@ -1269,7 +1547,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>41</v>
       </c>
@@ -1277,7 +1555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>42</v>
       </c>
@@ -1285,7 +1563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>43</v>
       </c>
@@ -1293,7 +1571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>44</v>
       </c>
@@ -1301,7 +1579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>45</v>
       </c>
@@ -1309,7 +1587,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>51</v>
       </c>
@@ -1317,7 +1595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>48</v>
       </c>
@@ -1325,7 +1603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
@@ -1333,7 +1611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>50</v>
       </c>
@@ -1341,31 +1619,223 @@
         <v>5</v>
       </c>
     </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B57" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B59" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B61" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B62" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B68" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B74" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" s="2">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B52"/>
+  <autoFilter ref="A1:B52" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1373,7 +1843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1381,7 +1851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1389,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -1397,7 +1867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1405,7 +1875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -1413,7 +1883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1421,7 +1891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>46</v>
       </c>
@@ -1429,7 +1899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
@@ -1437,7 +1907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
@@ -1445,7 +1915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
@@ -1453,7 +1923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>47</v>
       </c>
@@ -1461,7 +1931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1469,7 +1939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -1477,7 +1947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -1485,7 +1955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -1493,7 +1963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -1501,7 +1971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -1509,7 +1979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -1517,7 +1987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
@@ -1525,7 +1995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1533,7 +2003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1541,7 +2011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
@@ -1549,7 +2019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
@@ -1557,7 +2027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
@@ -1565,7 +2035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
@@ -1573,7 +2043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1581,7 +2051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
@@ -1589,7 +2059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
@@ -1597,7 +2067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
@@ -1605,7 +2075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
@@ -1613,7 +2083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
@@ -1621,7 +2091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
@@ -1629,7 +2099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>34</v>
       </c>
@@ -1637,7 +2107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>35</v>
       </c>
@@ -1645,7 +2115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
@@ -1653,7 +2123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -1661,7 +2131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
@@ -1669,7 +2139,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>39</v>
       </c>
@@ -1677,7 +2147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
@@ -1685,7 +2155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>52</v>
       </c>
@@ -1693,7 +2163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>49</v>
       </c>
@@ -1701,7 +2171,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>41</v>
       </c>
@@ -1709,7 +2179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>42</v>
       </c>
@@ -1717,7 +2187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>43</v>
       </c>
@@ -1725,7 +2195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>44</v>
       </c>
@@ -1733,7 +2203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>45</v>
       </c>
@@ -1741,7 +2211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>51</v>
       </c>
@@ -1749,7 +2219,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>48</v>
       </c>
@@ -1757,7 +2227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
@@ -1765,11 +2235,203 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B52" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B57" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B59" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B61" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B62" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B68" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B74" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B75" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B76" s="2">
         <v>5</v>
       </c>
     </row>
